--- a/results/Int Task Remove ACC 0.8/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 0.8/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.002187210059912452</v>
+        <v>-0.00021684567268232</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.00244792079797887</v>
+        <v>-0.001645358000431404</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.002711718684116746</v>
+        <v>-0.003023032858941868</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0002859660432314681</v>
+        <v>0.00103716967744471</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.003370909217287203</v>
+        <v>0.0004537979762057676</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.002363740327118914</v>
+        <v>0.0004155415856013622</v>
       </c>
       <c r="I3" t="n">
-        <v>3.104647726495102e-05</v>
+        <v>7.210511954796383e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001943116470673495</v>
+        <v>-0.0009048559930289225</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009477787174939311</v>
+        <v>0.008438764002871394</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007594630247085542</v>
+        <v>0.008428796025540598</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001646594017487563</v>
+        <v>0.000442196823403832</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.004245258717550017</v>
+        <v>-0.002241711964606146</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.004488404815317452</v>
+        <v>-0.0009471739768688559</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005810330947291582</v>
+        <v>0.00383927198421742</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006417346006557366</v>
+        <v>0.00465439517301604</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.001637594450475108</v>
+        <v>6.341702023413215e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.003870990509650006</v>
+        <v>-0.001447869176956483</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0003607015275764601</v>
+        <v>0.002807228582832922</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.005054548707843056</v>
+        <v>-0.002628891764743424</v>
       </c>
       <c r="V3" t="n">
-        <v>3.090783265939812e-05</v>
+        <v>-0.0001018707094138538</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.000290738109964217</v>
+        <v>0.000427026879595712</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0001833350894785824</v>
+        <v>-0.001056201500210218</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.0007655695831216625</v>
+        <v>-0.0003205541590334893</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.000219781076995944</v>
+        <v>0.0002468648308203336</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.0007046532897081991</v>
+        <v>0.000226542488923448</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0001807907273875997</v>
+        <v>-0.0003098177792311774</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.0006328827627665501</v>
+        <v>0.0005651855558745764</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.0006415539220467105</v>
+        <v>-0.001366290230825752</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.0003589010611025856</v>
+        <v>0.0006664552113346456</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.002432939442597277</v>
+        <v>-0.001657300600806152</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0001398807135694091</v>
+        <v>-9.874593950923493e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>8.682922177531082e-05</v>
+        <v>5.39665271917078e-05</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.002712845520782596</v>
+        <v>-0.0005841378588914582</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.0004035550899024986</v>
+        <v>-0.0009562969356506923</v>
       </c>
       <c r="AL3" t="n">
-        <v>-3.965598734257946e-05</v>
+        <v>6.111485876554745e-05</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0001927073092227194</v>
+        <v>-0.0001351380001882607</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0008373372810105495</v>
+        <v>-0.001200423769967574</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.0009674856294027911</v>
+        <v>0.000153803237167055</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0003244766093949747</v>
+        <v>-0.0001500617240169999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.000367973398848066</v>
+        <v>-0.0001305020597944173</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.001282826914469255</v>
+        <v>-0.000290978521335974</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.000432121593379774</v>
+        <v>-0.001065281598717765</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.0004282993484609764</v>
+        <v>0.001423909838142421</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.004570635988384427</v>
+        <v>-0.0005937708159739518</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.001762935910659151</v>
+        <v>-0.0007336997289600122</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.001269832865028127</v>
+        <v>-0.0009728038217769883</v>
       </c>
       <c r="AX3" t="n">
-        <v>-1.630494903435586e-05</v>
+        <v>5.415855979553853e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.002159254621390831</v>
+        <v>-5.194354991591935e-05</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.0005834307097792146</v>
+        <v>-0.001318523716700234</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.001825651171127684</v>
+        <v>-1.238074048917296e-05</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.000567426074327774</v>
+        <v>0.002192499937122512</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.0002769163909139083</v>
+        <v>-3.117001410285701e-05</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.0001155955477670068</v>
+        <v>0.0002047505376159175</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.00029754250877014</v>
+        <v>0.0005849414089683267</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.002986965135187004</v>
+        <v>0.003182111806275598</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.002136286351246338</v>
+        <v>-0.00103167307577557</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.0003989399401611293</v>
+        <v>-2.259610358330997e-05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.0009791945624962716</v>
+        <v>-0.0002659192945435395</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.0003409107612162232</v>
+        <v>-0.001221690733653306</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.0001542444846533597</v>
+        <v>0.000157641223320698</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.001119319590607173</v>
+        <v>-0.0006783309684193528</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.0007671644266040868</v>
+        <v>0.0008982520811049244</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0005594984807551565</v>
+        <v>-0.003328963251394176</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.0003941710153562938</v>
+        <v>-0.0002067384103064051</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.94444444444442e-05</v>
+        <v>-9.878115052541768e-06</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0004770606548212485</v>
+        <v>-0.0007645528938715329</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.001304397113000942</v>
+        <v>-0.0003846691902236532</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0002915961724413663</v>
+        <v>0.00154087488983358</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.0007916880844612029</v>
+        <v>7.737796848036435e-05</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.00054825444386019</v>
+        <v>-0.001557305551906085</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.0002362702774468995</v>
+        <v>-0.001570014150451629</v>
       </c>
       <c r="BX3" t="n">
-        <v>3.79222037351401e-05</v>
+        <v>-3.125381974333985e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.787752127863653e-05</v>
+        <v>0.0001859847443720208</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.494857730902079e-05</v>
+        <v>-6.923318234476375e-06</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.644736842104977e-05</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0003233626962629455</v>
+        <v>-9.969018570055155e-06</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.0004669076401314432</v>
+        <v>-0.001147206633483682</v>
       </c>
       <c r="CD3" t="n">
-        <v>-5.344735435595105e-06</v>
+        <v>-1.669175230154529e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>2.742208009976824e-05</v>
+        <v>0.0002704053827411568</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0003449515406197589</v>
+        <v>1.345803586251806e-05</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.0008055778826802663</v>
+        <v>-0.001305293278741099</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.0002606329338205693</v>
+        <v>-6.482380189550941e-05</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.0005288388672885869</v>
+        <v>-0.001380461333309161</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0.0004758846780265892</v>
+        <v>-0.0008131024095781291</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.000229597255872962</v>
+        <v>0.0007446224727025684</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004056005382274378</v>
+        <v>0.004169109221529414</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003655557395154582</v>
+        <v>0.006261257927217926</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005202973558148232</v>
+        <v>0.00590700549017768</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001920730148436426</v>
+        <v>0.003056955131450931</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007342555327325162</v>
+        <v>0.002985056239448244</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003042935624370844</v>
+        <v>0.003830116312716365</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001794163629690386</v>
+        <v>0.00021065266199204</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004315139916696489</v>
+        <v>0.006515927152078539</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01201456056901291</v>
+        <v>0.01231810370161124</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005206668780247955</v>
+        <v>0.009182868715817727</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002719684463457054</v>
+        <v>0.002953176689747107</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0100899338859755</v>
+        <v>0.007067876723670925</v>
       </c>
       <c r="O4" t="n">
-        <v>0.008184313325318876</v>
+        <v>0.004983637819018685</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01245137146748928</v>
+        <v>0.01307777328664925</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01227674520382122</v>
+        <v>0.01106886013095357</v>
       </c>
       <c r="R4" t="n">
-        <v>0.004953539674076226</v>
+        <v>0.004585992455112134</v>
       </c>
       <c r="S4" t="n">
-        <v>0.006340325246356896</v>
+        <v>0.005220259934087429</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003812587366863366</v>
+        <v>0.005951099818597105</v>
       </c>
       <c r="U4" t="n">
-        <v>0.008690080154249161</v>
+        <v>0.005894409210804108</v>
       </c>
       <c r="V4" t="n">
-        <v>4.30606534976091e-05</v>
+        <v>0.0001745655215560625</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002962187437170204</v>
+        <v>0.004815948323827196</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002953378690759173</v>
+        <v>0.003389538519071161</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002461655240763952</v>
+        <v>0.001847594441042999</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0009699039593538517</v>
+        <v>0.00169112847245686</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002250959242745413</v>
+        <v>0.002452440406094748</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0003936132355550314</v>
+        <v>0.0007692176462867883</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.002697994862932181</v>
+        <v>0.006635627406627222</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.004402263280496016</v>
+        <v>0.005403973879859269</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.003613051359309027</v>
+        <v>0.003590721460229757</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.00582359446154945</v>
+        <v>0.004309975893648094</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0004461052088638902</v>
+        <v>0.00046948699699036</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0007393075349210822</v>
+        <v>0.0003447817141994193</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.005512491432810125</v>
+        <v>0.00532148985778529</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.004379298966441884</v>
+        <v>0.005987602372129051</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0003866826709157525</v>
+        <v>0.0004064574233735475</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0003482503391847874</v>
+        <v>0.0008205486444349426</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002254695793074237</v>
+        <v>0.002509152456661626</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.002463441922094888</v>
+        <v>0.003993850483309243</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0007836846590715205</v>
+        <v>0.001011931351611686</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.001166065554093474</v>
+        <v>0.001271993864374874</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.003054962364321405</v>
+        <v>0.003522000516835504</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.001775958065075018</v>
+        <v>0.001850141198984894</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.003224596225017057</v>
+        <v>0.00388984117204853</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.006464537170003886</v>
+        <v>0.0122062618656492</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.002747739034250578</v>
+        <v>0.002059977712110989</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.003812119384327113</v>
+        <v>0.003204110861241199</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0002685646027784936</v>
+        <v>0.0003615191690169757</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.00501310007436969</v>
+        <v>0.004482434515579173</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.003303671453284579</v>
+        <v>0.00536307400675459</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.003006967768866453</v>
+        <v>0.01088865406712803</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.006251045999281129</v>
+        <v>0.009187484993396675</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0004036574864569662</v>
+        <v>0.0005486018536358004</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0005706541948688215</v>
+        <v>0.0005512282941793444</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.004429268187289464</v>
+        <v>0.006118705953468924</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.006642530254639867</v>
+        <v>0.01383257550471866</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.002922429580026688</v>
+        <v>0.002145546482193302</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0009464332967256571</v>
+        <v>0.0007113153443061334</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.003515951218383719</v>
+        <v>0.003595386256716899</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.002484841017850997</v>
+        <v>0.003154460296597831</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0004992441112037795</v>
+        <v>0.0009477000850405619</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.004621672294149232</v>
+        <v>0.002937271693147222</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.005305222351834233</v>
+        <v>0.003780877297072146</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0118203344849386</v>
+        <v>0.009418342399302487</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.002328166311666268</v>
+        <v>0.001619702379586696</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.00021960261528947</v>
+        <v>7.48061690808384e-05</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.001699967383400491</v>
+        <v>0.001319774712525914</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.003461478833962284</v>
+        <v>0.002406330489634847</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.00120341547722791</v>
+        <v>0.00266752469812506</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.003514065496419178</v>
+        <v>0.001654109774892229</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.001482981824008633</v>
+        <v>0.003971634017563049</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.002512526284605167</v>
+        <v>0.004201101215791022</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0002525102995008573</v>
+        <v>5.039571075432797e-05</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.00118437694819284</v>
+        <v>0.001013602550009806</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0004805219400939585</v>
+        <v>0.0007699198713712128</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>5.201114572644456e-05</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0009277117738329437</v>
+        <v>0.0003424586419418548</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.002414186810091163</v>
+        <v>0.001889646866988309</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.690153746749271e-05</v>
+        <v>4.437603571761137e-05</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0006322495744970954</v>
+        <v>0.0008586889952152888</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.003431068117819887</v>
+        <v>0.002451110231559053</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.004061103249469597</v>
+        <v>0.002473278569302474</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0003614622575722127</v>
+        <v>0.000709293161265934</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.002985107922238745</v>
+        <v>0.002266337418299874</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.002636016919301967</v>
+        <v>0.001744260030840268</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.001346945996504629</v>
+        <v>0.002898315568082109</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.009882478632478597</v>
+        <v>-0.005240963855421732</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.007794361525704774</v>
+        <v>-0.01437258153676069</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01411010154997329</v>
+        <v>-0.01427044361304121</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.002777777777777768</v>
+        <v>-0.004168893639764826</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.02297008547008539</v>
+        <v>-0.006522940851299131</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.006517094017093994</v>
+        <v>-0.008123997862105858</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0001583113456464336</v>
+        <v>-0.0001105583195135429</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.007055050774986671</v>
+        <v>-0.01330839123463392</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.001522593320235799</v>
+        <v>-0.002891566265060286</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0001096491228070762</v>
+        <v>-0.00154997327632278</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.002357563850687638</v>
+        <v>-0.00520628683693517</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.03210470085470084</v>
+        <v>-0.018407960199005</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0232371794871794</v>
+        <v>-0.01326699834162526</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01365131578947375</v>
+        <v>-0.01301571709233791</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.01843933725280599</v>
+        <v>-0.01656867985034743</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.01005732152162589</v>
+        <v>-0.005505077498663869</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0182692307692307</v>
+        <v>-0.01111111111111117</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.007116692830978521</v>
+        <v>-0.001977552111170566</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.02617521367521358</v>
+        <v>-0.01608765366114383</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.0005527915975677145</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.005009823182711237</v>
+        <v>-0.007465618860510814</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.005836373110995341</v>
+        <v>-0.007803313735970119</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.006959706959706924</v>
+        <v>-0.00411609498680734</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.002013752455795703</v>
+        <v>-0.0019884877027734</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.004133961276818398</v>
+        <v>-0.002897838899803518</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0004216867469879482</v>
+        <v>-0.00230844793713163</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.005540897097625286</v>
+        <v>-0.00807387862796829</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.009484106305367413</v>
+        <v>-0.009640437727983342</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.007139134966128213</v>
+        <v>-0.004422332780541771</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.016559829059829</v>
+        <v>-0.008910891089108941</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.0007295466388744342</v>
+        <v>-0.001042209484106338</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.0009419152276294862</v>
+        <v>-0.0004807692307692291</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01197220737573491</v>
+        <v>-0.01047568145376807</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.006080707573244859</v>
+        <v>-0.01265892758430077</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.000844327176780979</v>
+        <v>-0.0007186290768380288</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.0003206841261357174</v>
+        <v>-0.00179419525065958</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.001794195250659592</v>
+        <v>-0.005910290237466964</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.006461698801459126</v>
+        <v>-0.005002605523710302</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.0007831325301204672</v>
+        <v>-0.001746987951807266</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.001129666011787822</v>
+        <v>-0.001465201465201427</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.005940594059405979</v>
+        <v>-0.007075732448866856</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.003799472295514483</v>
+        <v>-0.005329815303430019</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.004591029023746651</v>
+        <v>-0.001282051282051277</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.01316306483300593</v>
+        <v>-0.02079155672823214</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.006730769230769207</v>
+        <v>-0.006227106227106216</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.01145996860282572</v>
+        <v>-0.008948194662480369</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.0005277044854881008</v>
+        <v>-0.0004709576138147265</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.01243781094527358</v>
+        <v>-0.00779696493982206</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.007378335949764503</v>
+        <v>-0.01393034825870651</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.005077498663816149</v>
+        <v>-0.02058047493403688</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.009882478632478597</v>
+        <v>-0.01132530120481931</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0008840864440078589</v>
+        <v>-0.0007326007326006967</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.00101549973276317</v>
+        <v>-0.0006279434850863019</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.01113456464379944</v>
+        <v>-0.01060686015831127</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.005843373493975901</v>
+        <v>-0.01662650602409641</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.006907378335949743</v>
+        <v>-0.006578220011055902</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.002585751978891748</v>
+        <v>-0.001480263157894779</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.01020408163265303</v>
+        <v>-0.005023547880690727</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.00317873892652426</v>
+        <v>-0.008548812664907613</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.0008858780614904082</v>
+        <v>-0.000641368252271457</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.01355311355311353</v>
+        <v>-0.008163265306122436</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.007968337730870656</v>
+        <v>-0.003614457831325335</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.01736147757255931</v>
+        <v>-0.02506596306068596</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.00427305888483589</v>
+        <v>-0.002929795467108887</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>-0.0001603420630678531</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.00169956140350882</v>
+        <v>-0.003040353786622463</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.002825745682888525</v>
+        <v>-0.006565919749869742</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.001674515960230216</v>
+        <v>-0.001046572475143892</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.005471599791558135</v>
+        <v>-0.002511773940345352</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.001206140350877227</v>
+        <v>-0.01166390270867889</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.001883830455259006</v>
+        <v>-0.01227197346600337</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.0003647733194371949</v>
+        <v>-0.0001096491228070207</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.00131926121372028</v>
+        <v>-0.0009086050240513565</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.0006860158311345454</v>
+        <v>-0.001517530088958641</v>
       </c>
       <c r="CA5" t="n">
         <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.0005732152162584824</v>
+        <v>-0.0005402750491159236</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.00407662082514737</v>
+        <v>-0.004201216141514685</v>
       </c>
       <c r="CD5" t="n">
-        <v>-5.344735435595105e-05</v>
+        <v>-0.0001068947087119021</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.001098901098901051</v>
+        <v>-0.0002616431187859591</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.008806670140698325</v>
+        <v>-0.00526315789473687</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.003296703296703296</v>
+        <v>-0.005523710265763449</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.0008895866038722833</v>
+        <v>-0.00104657247514387</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.007517965726920916</v>
+        <v>-0.005054715997915604</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.00580847723704866</v>
+        <v>-0.003537866224433406</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.0015899122807018</v>
+        <v>-0.001831501831501814</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.004415433895467502</v>
+        <v>-0.003252670121686199</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.005008526737381613</v>
+        <v>-0.004443788177875873</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.005085444051328891</v>
+        <v>-0.00711090023456766</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.001418504053627634</v>
+        <v>-0.0007110230561177433</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.003083723338013059</v>
+        <v>-0.0005259499536608064</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.004400673643630046</v>
+        <v>-0.0002301513747296979</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-5.314625850340038e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009028655261026697</v>
+        <v>-0.00421584536458168</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002239866100311933</v>
+        <v>0.0003070510536438142</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003914342739297655</v>
+        <v>0.0007417657997834727</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0003237828419927147</v>
+        <v>-0.0006012827365045742</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.002976757777378161</v>
+        <v>-0.002267274225105581</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.006979809489008232</v>
+        <v>-0.0006856513193057912</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001336612122956549</v>
+        <v>-0.003794426685761562</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001147118238206418</v>
+        <v>0.0009068265082076921</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.005698816108903801</v>
+        <v>-0.001888140803199362</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.006407931152900406</v>
+        <v>-0.002737926853909884</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.00309897250269068</v>
+        <v>-9.559868069428657e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.004376660499252357</v>
+        <v>-0.004670446390294486</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.0001555704444018202</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.001817031604745378</v>
+        <v>-0.00247691149806134</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.001532224646505637</v>
+        <v>-0.00219416994920617</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.001460424019178061</v>
+        <v>-0.0007017953937558136</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0005713876349867808</v>
+        <v>-0.0002825423633041918</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.00238968214049832</v>
+        <v>-0.001523474979554812</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>-0.0004333501832021275</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0026681347188344</v>
+        <v>-0.002380818407066243</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.002697230044326715</v>
+        <v>-0.00597265619646702</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.0009869153207868297</v>
+        <v>-0.0008684409932071229</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.002391769107429179</v>
+        <v>-0.005119977344703577</v>
       </c>
       <c r="AG6" t="n">
-        <v>-2.375477922769431e-05</v>
+        <v>-0.0002526272916358346</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0002072968490878929</v>
+        <v>-0.0001807228915662873</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.007923146988697276</v>
+        <v>-0.002619429181929164</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.004514751829433982</v>
+        <v>-0.002155444542429963</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0001473477406679913</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.670940170940161e-05</v>
+        <v>-0.0004810261892036593</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.0002805986103688013</v>
+        <v>-0.002347585908049787</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.001878636425140368</v>
+        <v>-0.002098318314006298</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0002747252747252571</v>
+        <v>-0.0005233943181767592</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.0001940847301552473</v>
+        <v>-0.0007399933723104713</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.003453356504972577</v>
+        <v>-0.00146970231650882</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.036144578310756e-05</v>
+        <v>-0.001476103582962385</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.0006668627285764229</v>
+        <v>-0.0006725508077123799</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.01060635620190836</v>
+        <v>-0.005966922205121974</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.002783567830467285</v>
+        <v>-0.001005964648065982</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.001505226997620718</v>
+        <v>-0.0009810954343690893</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0001047289883119251</v>
+        <v>-8.22368421052655e-05</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.002697632311377701</v>
+        <v>-0.0003741457559603145</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.002369082155662542</v>
+        <v>-0.002617583483291405</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.004081987146083071</v>
+        <v>-0.003647667593450771</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.002580729697626663</v>
+        <v>-0.003018190944099578</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.000574323514095032</v>
+        <v>-0.0002804701311515778</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.000237467018469642</v>
+        <v>-4.111842105265218e-05</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0006969813270274101</v>
+        <v>-0.00124950350853964</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.001270044520658975</v>
+        <v>-0.006183533418300996</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.003803438081435789</v>
+        <v>-0.001337736097604761</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.0007934369055168228</v>
+        <v>-0.0001962323390894694</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.001391828884075541</v>
+        <v>-0.001812243312048209</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.001803676903890694</v>
+        <v>-0.001010596546310824</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0004497333978274093</v>
+        <v>-0.000529981769182028</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.0011692287649818</v>
+        <v>-0.00119491776232937</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.002899426183265039</v>
+        <v>-0.001862026862026839</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.004816681470835288</v>
+        <v>-0.004987467239347589</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.001706923759252774</v>
+        <v>-0.00128105840864492</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.0004586536411929132</v>
+        <v>-0.001149631420418548</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.0006527784958467037</v>
+        <v>-0.0004071531892188534</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0004420432220039489</v>
+        <v>6.024096385541244e-05</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.002498307526732443</v>
+        <v>-0.0008195480768328877</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.000699514563616549</v>
+        <v>-0.001961735789461507</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.00107041748163316</v>
+        <v>-0.001858526259529158</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>-7.367387033399564e-05</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.0005745305083894258</v>
+        <v>-0.0001877543437696111</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0002805986103688013</v>
+        <v>-0.0001740482034187863</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.000223431143652883</v>
+        <v>-0.0001451516841554395</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.001705348603336268</v>
+        <v>-0.002674553126565252</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-3.908285565398517e-05</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0002812625748573938</v>
+        <v>-0.0001037232843721314</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.001189365809769677</v>
+        <v>-0.0005118821775307758</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.001839544854881303</v>
+        <v>-0.002501295198523334</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0004604854465937225</v>
+        <v>-0.0004509383688600654</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.001320276108025201</v>
+        <v>-0.003024753803591851</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.001815210167655937</v>
+        <v>-0.002230025145668555</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.0005915369947046472</v>
+        <v>-0.000599136704471856</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0008814556971867727</v>
+        <v>-8.01282051281993e-05</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.001923833949660042</v>
+        <v>-0.0005682988363711506</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.001973141393086708</v>
+        <v>-0.001088549448453447</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0003735013655510766</v>
+        <v>0.0005309462598381165</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0004695396417275455</v>
+        <v>0.0006058447996006633</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.002645438408581857</v>
+        <v>0.001178046892965656</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001976351244853835</v>
+        <v>-0.001995660743236804</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00616159453420308</v>
+        <v>0.00497286416660681</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006449359443049257</v>
+        <v>0.008950586977393694</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0008488656608709843</v>
+        <v>0.001243435279579824</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0007238878625350609</v>
+        <v>-5.41157944312809e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0007632024624419641</v>
+        <v>0.0005509794279157209</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00723144314296204</v>
+        <v>0.0003320175410353398</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.005908296564971038</v>
+        <v>0.004938391079942612</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001843723924858765</v>
+        <v>-0.0001506024096386005</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.002651794513144917</v>
+        <v>-0.001124197484754624</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0003145685784381791</v>
+        <v>0.0001170708474925286</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.00277377957670556</v>
+        <v>-0.001615153291644988</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0004726357097129096</v>
+        <v>0.0004278072423448964</v>
       </c>
       <c r="X7" t="n">
-        <v>8.017103153394321e-05</v>
+        <v>8.015675606536377e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>-5.341880341880323e-05</v>
+        <v>0.0001850604200198669</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.341880341880323e-05</v>
+        <v>0.000227518772201929</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.0006127216481694008</v>
+        <v>-0.0002912099993234385</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.0003949350031705933</v>
+        <v>-0.0009737586383114727</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.0009286696885641265</v>
+        <v>-5.389811517584329e-05</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.0005878066941669424</v>
+        <v>-0.0002239798316730546</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.001080496083055826</v>
+        <v>-0.001157382740951457</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0001404119953893557</v>
+        <v>-2.45579567780041e-05</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.763957987838572e-05</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0002037727242096221</v>
+        <v>-0.000374582241311583</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.0004436495771045379</v>
+        <v>-0.0003170877177139597</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0002088781959250108</v>
+        <v>5.221954898125825e-05</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0006704429658934308</v>
+        <v>-0.00124377789082577</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.000962052378407241</v>
+        <v>8.121838478981626e-05</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0002368070441261749</v>
+        <v>-0.0002037727242095999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.017103153393212e-05</v>
+        <v>-0.0003740172767430661</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.001161416785409381</v>
+        <v>-7.923639548370608e-05</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0003804428711145225</v>
+        <v>-0.0006412683239914785</v>
       </c>
       <c r="AT7" t="n">
-        <v>-8.017103153393212e-05</v>
+        <v>-0.0004445628585963313</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.004126472723397728</v>
+        <v>-0.001599752586594716</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.001527620416679343</v>
+        <v>-5.344735435595105e-05</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.000166527797065219</v>
+        <v>-0.0007747582306641798</v>
       </c>
       <c r="AX7" t="n">
-        <v>-2.672367717798108e-05</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0006366891717442368</v>
+        <v>0.0002541003136007303</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-2.754414095101925e-06</v>
+        <v>0.000113688318211369</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.002549751243781084</v>
+        <v>-0.001723656289227332</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0001206285006712104</v>
+        <v>0.0005581863312126345</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0.0001580904332506239</v>
+        <v>-0.0001043950733127685</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0001973023673641661</v>
+        <v>0.0001227897838899872</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0002540289362578496</v>
+        <v>-0.0003213727296595526</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.00190523429152446</v>
+        <v>0.002401523039837194</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.000820106503980994</v>
+        <v>-0.0005845363688797622</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-2.455795677799855e-05</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-1.665334536937735e-17</v>
+        <v>-0.0008024405313562189</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.0002891329050393853</v>
+        <v>-0.0001595001081674152</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.0001381978993919286</v>
+        <v>-0.0001068518823061859</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0001603420630678753</v>
+        <v>-6.793609499489142e-06</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0006448112698903774</v>
+        <v>-0.0004275788348476861</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0001181039949270545</v>
+        <v>-0.002866358943118019</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.0004334802502326872</v>
+        <v>0.0002210216110019647</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>2.670940170940161e-05</v>
+        <v>-0.0006765403559278627</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0006142876883791392</v>
+        <v>0.0003677886318121159</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0001062178029048011</v>
+        <v>0.0004303939348143715</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0.0007676499623689103</v>
+        <v>-0.0004542025837456221</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0006303735214402751</v>
+        <v>-0.0006262651821862475</v>
       </c>
       <c r="BW7" t="n">
-        <v>-0.0003322477605138763</v>
+        <v>-0.0006888821721827698</v>
       </c>
       <c r="BX7" t="n">
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-9.823182711199974e-05</v>
+        <v>0</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.670940170940161e-05</v>
+        <v>-2.45579567780152e-05</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-5.277044854880008e-05</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0.0004762878485535971</v>
+        <v>-0.0004496991104133874</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>2.604677137085787e-05</v>
+        <v>0</v>
       </c>
       <c r="CF7" t="n">
-        <v>-7.948242801019689e-05</v>
+        <v>-7.942532613587906e-05</v>
       </c>
       <c r="CG7" t="n">
-        <v>5.336170154451869e-05</v>
+        <v>-0.001254125305897386</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0001569913969594328</v>
+        <v>-2.638522427439449e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>5.277044854882785e-05</v>
+        <v>-0.0002727321879822164</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0.0004185976366055221</v>
+        <v>-0.0002610977449062745</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0.0001569858712715422</v>
+        <v>-0.0004055611785875157</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0005643618667191319</v>
+        <v>0.001636053131465012</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0006590256953778795</v>
+        <v>0.0008049185668212167</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001040136443010209</v>
+        <v>0.0006008758856500873</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0001197556748021494</v>
+        <v>0.002915345562061103</v>
       </c>
       <c r="G8" t="n">
-        <v>9.036144578311867e-05</v>
+        <v>0.002239049719077885</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0006225589982720964</v>
+        <v>0.002194579685714721</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>7.915567282323343e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003101804993252424</v>
+        <v>0.004790034658578413</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01239016856996506</v>
+        <v>0.009743215352942803</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01147424247530801</v>
+        <v>0.01231068152854815</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002314912424602028</v>
+        <v>0.001564786735634635</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0006664655950562009</v>
+        <v>0.0009830981987936499</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0006896105286303217</v>
+        <v>0.00151253057537393</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01516675636767791</v>
+        <v>0.01247296929731913</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01473577000308932</v>
+        <v>0.008084772370486637</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001602705286667872</v>
+        <v>8.012820512821594e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0003983219210806466</v>
+        <v>0.0003352732793522134</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001723210318559107</v>
+        <v>0.003627416056741386</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.001125602692956895</v>
+        <v>-3.924646781789387e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>5.3256714701308e-05</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001118203925655684</v>
+        <v>0.003178710711475288</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002256666192741152</v>
+        <v>0.0009477620243507428</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0005756578947367919</v>
+        <v>0.0003739601748687815</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0002715551659491472</v>
+        <v>0.0005208761597390532</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0009954951384485127</v>
+        <v>0.001508019740358352</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0004595626815292019</v>
+        <v>9.198550124716321e-05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.001670129895343736</v>
+        <v>0.001149039603575991</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.001034688853646379</v>
+        <v>0.001092777683429819</v>
       </c>
       <c r="AE8" t="n">
-        <v>-3.358835456702402e-05</v>
+        <v>0.00144964094832174</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0004523026315788964</v>
+        <v>0.001478359410135638</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0004658496505115517</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0004442473599586549</v>
+        <v>0.0002496796934454426</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.001351161223842714</v>
+        <v>0.00176543198677111</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.002566812718496067</v>
+        <v>0.001747027688590805</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.111842105261609e-05</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.00031728692065984</v>
+        <v>0.0001476045883940486</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.001009778911564649</v>
+        <v>-0.0003740030012744977</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0006792376161587565</v>
+        <v>0.0007085465874050734</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0007315396700706938</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.001070978808407122</v>
+        <v>-1.032905285686109e-06</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0005509597921669135</v>
+        <v>0.0008608127859029396</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.00121416608141231</v>
+        <v>3.298498841637632e-05</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.00140664314272908</v>
+        <v>0.002763131729688961</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0005666401188031244</v>
+        <v>0.003079620616079371</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.0001501516488186944</v>
+        <v>0.0002748114560081255</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0003969264237774245</v>
+        <v>-0.0001596267190569794</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.314625850340038e-05</v>
+        <v>7.915567282323343e-05</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.00112458733424626</v>
+        <v>0.0008205095935749889</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.001798411721542348</v>
+        <v>0.001269037663929606</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0.0005275334404579307</v>
+        <v>0.005527882974873305</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.003262599421972975</v>
+        <v>0.005180567262860198</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.008551576697162e-05</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0005238594130718283</v>
+        <v>0.0006049348683145495</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.001381114186565302</v>
+        <v>0.0002877951152754743</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.006585184143819561</v>
+        <v>0.007754336418157351</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.0004007695048582449</v>
+        <v>9.070176985206678e-05</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>8.017103153393489e-05</v>
+        <v>0.0002578585461689598</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.001019608155802224</v>
+        <v>-4.145936981757858e-05</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0001293601144314399</v>
+        <v>0.0004821287377709038</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0002125994912095086</v>
+        <v>0.00027331417568347</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001586159532596598</v>
+        <v>0.0008265725015477621</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.003465216465074433</v>
+        <v>0.003171105356321977</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.006467129877071084</v>
+        <v>0.0005477782802742943</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0007746440269155775</v>
+        <v>0.001082020389249291</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.001331838998409424</v>
+        <v>0.0002941275962384194</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.002032506273194925</v>
+        <v>0.0008064416048873008</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.001197417876634751</v>
+        <v>0.002093285654770149</v>
       </c>
       <c r="BU8" t="n">
-        <v>-0.000146980224478882</v>
+        <v>0.001064809335574138</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001102526895437378</v>
+        <v>6.41971339045283e-05</v>
       </c>
       <c r="BW8" t="n">
-        <v>-2.605523710265123e-05</v>
+        <v>0.0002826039305947603</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0003146984106305206</v>
+        <v>0.0001052109099258874</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0002179479534756279</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0007478775233318496</v>
+        <v>0.0001827166468903435</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0002859534435224714</v>
+        <v>0.0002898947579397265</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0001634407789248449</v>
+        <v>8.223684210524051e-05</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.002066329784879967</v>
+        <v>0.0008027625011921419</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.001218587146064426</v>
+        <v>0.0001201708944894464</v>
       </c>
       <c r="CH8" t="n">
-        <v>0</v>
+        <v>0.0001877543437696028</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001376269374665964</v>
+        <v>-0.0001304469615501264</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.001838922855601557</v>
+        <v>-5.344735435598158e-05</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0005762472968798421</v>
+        <v>0.0005001593761469969</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003022407503908242</v>
+        <v>0.008693516699410597</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002005277044854925</v>
+        <v>0.009037328094302566</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004939759036144587</v>
+        <v>0.004322200392927311</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003924646781789653</v>
+        <v>0.006909894969596431</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002110817941952536</v>
+        <v>0.004469548133595291</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003474078033137418</v>
+        <v>0.00574903261470423</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0005211047420531356</v>
+        <v>0.0005482456140350033</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008693516699410587</v>
+        <v>0.008055009823182713</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0363782051282052</v>
+        <v>0.03376758728504427</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01606488749345895</v>
+        <v>0.02876498176133401</v>
       </c>
       <c r="M9" t="n">
-        <v>0.006566265060240983</v>
+        <v>0.005317982456140314</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001354872329338164</v>
+        <v>0.006581532416502944</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002354788069073788</v>
+        <v>0.003683693516699415</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02240750390828553</v>
+        <v>0.03027618551328813</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02511773940345371</v>
+        <v>0.02245961438249087</v>
       </c>
       <c r="R9" t="n">
-        <v>0.004201216141514741</v>
+        <v>0.01149312377210215</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003663003663003683</v>
+        <v>0.009184675834970523</v>
       </c>
       <c r="T9" t="n">
-        <v>0.005367378843147442</v>
+        <v>0.01516414799374672</v>
       </c>
       <c r="U9" t="n">
-        <v>0.00417485265225932</v>
+        <v>0.00677799607072691</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0001046572475143837</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.005013192612137229</v>
+        <v>0.008389786347055728</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003349031920460521</v>
+        <v>0.002357456140350822</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001768933112216753</v>
+        <v>0.002905701754385925</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001326699834162581</v>
+        <v>0.004256495301271401</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.00219134152859437</v>
+        <v>0.005140961857379745</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0009086050240512788</v>
+        <v>0.000274122807017485</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.002501302761855073</v>
+        <v>0.01459369817578766</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.007017543859649067</v>
+        <v>0.005701754385964874</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.005921052631578905</v>
+        <v>0.008004385964912254</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.004096385542168702</v>
+        <v>0.004111842105263131</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0006633499170812685</v>
+        <v>0.0007186290768380288</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001626506024096386</v>
+        <v>0.0007127192982455344</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.00313971742543172</v>
+        <v>0.009210526315789424</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.005361445783132535</v>
+        <v>0.008991228070175383</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0005211047420531356</v>
+        <v>0.0008443271767810789</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0008443271767810901</v>
+        <v>0.001227897838899816</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.006670140698280325</v>
+        <v>0.003335070349140157</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.002590361445783129</v>
+        <v>0.009978070175438558</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001603420630678831</v>
+        <v>0.002266445550027629</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.002721088435374175</v>
+        <v>0.003150912106135972</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.003734939759036127</v>
+        <v>0.006743421052631549</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.002939604489577819</v>
+        <v>0.00103143418467585</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.007469879518072287</v>
+        <v>0.01127694859038137</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.005158936946326187</v>
+        <v>0.02146951537258989</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.002266445550027696</v>
+        <v>0.001055408970976313</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.002405130946018197</v>
+        <v>0.002691292875989482</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0005732152162584492</v>
+        <v>0.000834970530451884</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.001445783132530132</v>
+        <v>0.006826472120896265</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.00343007915567286</v>
+        <v>0.004116094986807439</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.004337349397590362</v>
+        <v>0.02172470978441127</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.01111704970603954</v>
+        <v>0.02209484106305365</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0002084418968212542</v>
+        <v>0.001302761855132861</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0008372579801151359</v>
+        <v>0.001146430432516898</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.005627931214173987</v>
+        <v>0.01265892758430066</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.01560662747194014</v>
+        <v>0.02493090105030403</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.001626506024096375</v>
+        <v>0.001265060240963811</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0008895866038723166</v>
+        <v>0.00130276185513285</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.001899736147757303</v>
+        <v>0.008759894459102958</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.005602409638554229</v>
+        <v>0.001710315339390656</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0006802721088435271</v>
+        <v>0.002240750390828538</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.00235042735042742</v>
+        <v>0.002813965607086999</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.009733124018838324</v>
+        <v>0.007075732448866745</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.01943720687858257</v>
+        <v>0.01271495570609689</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.004216867469879504</v>
+        <v>0.001563314226159429</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.000694444444444442</v>
+        <v>0.0001055408970976446</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.00403614457831325</v>
+        <v>0.0007482629609834701</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.009578313253012061</v>
+        <v>0.001934770591487001</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.002136529442417878</v>
+        <v>0.008291873963515717</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.007590361445783134</v>
+        <v>0.003372028745163058</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.003493975903614466</v>
+        <v>0.003022407503908253</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.006746987951807237</v>
+        <v>0.002902374670184749</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0005421686746987619</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.002650602409638558</v>
+        <v>0.002819237147595344</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.0009419152276295307</v>
+        <v>0.001603095632946372</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>0.0001644736842104977</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.002469879518072293</v>
+        <v>0.0006080707573244859</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.004578313253012045</v>
+        <v>0.001024096385542139</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>5.232862375719183e-05</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001354872329338153</v>
+        <v>0.002598120508568258</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.003151709401709502</v>
+        <v>0.004809286898839115</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.01096385542168673</v>
+        <v>0.002849604221635937</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0001603420630678864</v>
+        <v>0.001381978993919286</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.002530120481927722</v>
+        <v>0.002058047493403747</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.002512025654730132</v>
+        <v>0.002216358839050192</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.002779262426509921</v>
+        <v>0.006522940851299031</v>
       </c>
     </row>
   </sheetData>
